--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/SOUTH_CAROLINA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/SOUTH_CAROLINA_2015.xlsx
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C155">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C263">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C752">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C753">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C807">
